--- a/Matlab/EQD2_with_tolerances_090126.xlsx
+++ b/Matlab/EQD2_with_tolerances_090126.xlsx
@@ -5,23 +5,22 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\Physics\Brachytherapy\HDR\_PATIENTS\zzLibraryCases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\Physics\Faculty\Brook Byrd\Projects\Embrace_DVH_Eval\Script\Embrace_DVH_Eval\Matlab\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="135" yWindow="30" windowWidth="15135" windowHeight="9300" tabRatio="332" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="FX1-4 HIPO" sheetId="8" r:id="rId1"/>
-    <sheet name="FX1-4 Clinical_GP" sheetId="7" r:id="rId2"/>
-    <sheet name="FX1-4_Goal" sheetId="2" r:id="rId3"/>
+    <sheet name="FX1-4 Clinical_GP" sheetId="7" r:id="rId1"/>
+    <sheet name="FX1-4_Goal" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="104">
   <si>
     <t>BT</t>
   </si>
@@ -986,9 +985,6 @@
   </si>
   <si>
     <t>25</t>
-  </si>
-  <si>
-    <t>PEREIRA, GABRIELA 26926238</t>
   </si>
   <si>
     <t>Planning Goal</t>
@@ -1365,7 +1361,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1605,275 +1601,16 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="14" fontId="8" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="93">
-    <dxf>
-      <font>
-        <strike val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="62">
     <dxf>
       <font>
         <strike val="0"/>
@@ -2727,9 +2464,7 @@
         <v>29</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="5" t="s">
-        <v>89</v>
-      </c>
+      <c r="C3" s="5"/>
       <c r="D3" s="51"/>
       <c r="E3" s="51"/>
       <c r="F3" s="51"/>
@@ -2932,8 +2667,8 @@
       <c r="B15" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="27">
-        <v>46265</v>
+      <c r="C15" s="99" t="s">
+        <v>42</v>
       </c>
       <c r="D15" s="27"/>
       <c r="E15" s="27" t="s">
@@ -3449,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="K38" s="25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L38" s="25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3518,10 +3253,10 @@
         <v>133.84320000000002</v>
       </c>
       <c r="K40" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="L40" s="49" t="s">
         <v>93</v>
-      </c>
-      <c r="L40" s="49" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:12" s="14" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
@@ -3623,10 +3358,10 @@
         <v>79.236666666666679</v>
       </c>
       <c r="K44" s="49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L44" s="49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3694,10 +3429,10 @@
         <v>87.418299999999988</v>
       </c>
       <c r="K46" s="97" t="s">
+        <v>90</v>
+      </c>
+      <c r="L46" s="49" t="s">
         <v>91</v>
-      </c>
-      <c r="L46" s="49" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3860,10 +3595,10 @@
         <v>58.88</v>
       </c>
       <c r="K52" s="49" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L52" s="49" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3960,10 +3695,10 @@
         <v>0</v>
       </c>
       <c r="K56" s="25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L56" s="25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4154,10 +3889,10 @@
         <v>69.342479999999995</v>
       </c>
       <c r="K62" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="L62" s="49" t="s">
         <v>97</v>
-      </c>
-      <c r="L62" s="49" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="63" spans="1:12" s="14" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
@@ -4262,10 +3997,10 @@
         <v>73.759680000000003</v>
       </c>
       <c r="K66" s="49" t="s">
+        <v>98</v>
+      </c>
+      <c r="L66" s="49" t="s">
         <v>99</v>
-      </c>
-      <c r="L66" s="49" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4400,10 +4135,10 @@
         <v>65.512079999999997</v>
       </c>
       <c r="K70" s="49" t="s">
+        <v>98</v>
+      </c>
+      <c r="L70" s="49" t="s">
         <v>99</v>
-      </c>
-      <c r="L70" s="49" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="71" spans="1:12" s="14" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
@@ -4575,10 +4310,10 @@
         <v>66.938000000000002</v>
       </c>
       <c r="K76" s="49" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L76" s="49" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="77" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4744,2628 +4479,10 @@
         <v>68.871679999999998</v>
       </c>
       <c r="K82" s="49" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L82" s="49" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A83" s="16"/>
-      <c r="B83" s="16"/>
-      <c r="C83" s="19"/>
-      <c r="D83" s="19"/>
-      <c r="E83" s="19"/>
-      <c r="F83" s="19"/>
-      <c r="G83" s="19"/>
-      <c r="H83" s="19"/>
-      <c r="I83" s="54"/>
-      <c r="J83" s="30"/>
-    </row>
-    <row r="84" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A84" s="16"/>
-      <c r="B84" s="16"/>
-      <c r="C84" s="19"/>
-      <c r="D84" s="19"/>
-      <c r="E84" s="19"/>
-      <c r="F84" s="19"/>
-      <c r="G84" s="19"/>
-      <c r="H84" s="19"/>
-      <c r="I84" s="54"/>
-      <c r="J84" s="30"/>
-    </row>
-    <row r="85" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A85" s="16"/>
-      <c r="B85" s="16"/>
-      <c r="C85" s="19"/>
-      <c r="D85" s="19"/>
-      <c r="E85" s="19"/>
-      <c r="F85" s="19"/>
-      <c r="G85" s="19"/>
-      <c r="H85" s="19"/>
-      <c r="I85" s="54"/>
-      <c r="J85" s="30"/>
-    </row>
-    <row r="86" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B86" s="16"/>
-      <c r="C86" s="19"/>
-      <c r="D86" s="19"/>
-      <c r="E86" s="19"/>
-      <c r="F86" s="19"/>
-      <c r="G86" s="19"/>
-      <c r="H86" s="19"/>
-      <c r="I86" s="54"/>
-      <c r="J86" s="30"/>
-    </row>
-    <row r="87" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="7"/>
-      <c r="B87" s="16"/>
-      <c r="C87" s="19"/>
-      <c r="D87" s="19"/>
-      <c r="E87" s="19"/>
-      <c r="F87" s="19"/>
-      <c r="G87" s="19"/>
-      <c r="H87" s="19"/>
-      <c r="I87" s="54"/>
-      <c r="J87" s="30"/>
-    </row>
-    <row r="88" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="I88" s="14"/>
-      <c r="J88" s="14"/>
-    </row>
-    <row r="89" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="E89" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A90" s="16"/>
-      <c r="B90" s="16"/>
-      <c r="C90" s="19"/>
-      <c r="D90" s="19"/>
-      <c r="E90" s="19"/>
-      <c r="F90" s="19"/>
-      <c r="G90" s="19"/>
-      <c r="H90" s="19"/>
-      <c r="I90" s="54"/>
-      <c r="J90" s="30"/>
-    </row>
-    <row r="91" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="J91" s="95" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="A92" s="84" t="s">
-        <v>80</v>
-      </c>
-      <c r="B92" s="85"/>
-      <c r="C92" s="36"/>
-      <c r="D92" s="42">
-        <f>C92</f>
-        <v>0</v>
-      </c>
-      <c r="E92" s="36"/>
-      <c r="F92" s="36">
-        <f>E92</f>
-        <v>0</v>
-      </c>
-      <c r="G92" s="36"/>
-      <c r="H92" s="36"/>
-      <c r="I92" s="66">
-        <f>AVERAGE(C92:H92)</f>
-        <v>0</v>
-      </c>
-      <c r="J92" s="67">
-        <f>STDEVP(C92:H92)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A93" s="15"/>
-      <c r="B93" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C93" s="47">
-        <v>6.66</v>
-      </c>
-      <c r="D93" s="47">
-        <f>C93</f>
-        <v>6.66</v>
-      </c>
-      <c r="E93" s="47">
-        <f t="shared" ref="E93:F93" si="35">D93</f>
-        <v>6.66</v>
-      </c>
-      <c r="F93" s="47">
-        <f t="shared" si="35"/>
-        <v>6.66</v>
-      </c>
-      <c r="G93" s="42"/>
-      <c r="H93" s="42"/>
-      <c r="I93" s="56"/>
-      <c r="J93" s="86"/>
-    </row>
-    <row r="94" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="15"/>
-      <c r="B94" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="C94" s="38">
-        <f t="shared" ref="C94:H94" si="36">C93*(1+C93/3)*0.6</f>
-        <v>12.867120000000002</v>
-      </c>
-      <c r="D94" s="38">
-        <f t="shared" si="36"/>
-        <v>12.867120000000002</v>
-      </c>
-      <c r="E94" s="38">
-        <f t="shared" si="36"/>
-        <v>12.867120000000002</v>
-      </c>
-      <c r="F94" s="38">
-        <f t="shared" si="36"/>
-        <v>12.867120000000002</v>
-      </c>
-      <c r="G94" s="38">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="H94" s="38">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="I94" s="40">
-        <f>SUM(C94:H94)</f>
-        <v>51.468480000000007</v>
-      </c>
-      <c r="J94" s="40">
-        <f>I94+G$9</f>
-        <v>94.668480000000002</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A95" s="15"/>
-      <c r="B95" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C95" s="47">
-        <v>3.53</v>
-      </c>
-      <c r="D95" s="47">
-        <f>C95</f>
-        <v>3.53</v>
-      </c>
-      <c r="E95" s="47">
-        <f t="shared" ref="E95:F95" si="37">D95</f>
-        <v>3.53</v>
-      </c>
-      <c r="F95" s="47">
-        <f t="shared" si="37"/>
-        <v>3.53</v>
-      </c>
-      <c r="G95" s="42"/>
-      <c r="H95" s="42"/>
-      <c r="I95" s="56"/>
-      <c r="J95" s="86"/>
-    </row>
-    <row r="96" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="15"/>
-      <c r="B96" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="C96" s="38">
-        <f t="shared" ref="C96:H96" si="38">C95*(1+C95/3)*0.6</f>
-        <v>4.6101799999999997</v>
-      </c>
-      <c r="D96" s="38">
-        <f t="shared" si="38"/>
-        <v>4.6101799999999997</v>
-      </c>
-      <c r="E96" s="38">
-        <f t="shared" si="38"/>
-        <v>4.6101799999999997</v>
-      </c>
-      <c r="F96" s="38">
-        <f t="shared" si="38"/>
-        <v>4.6101799999999997</v>
-      </c>
-      <c r="G96" s="38">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="H96" s="38">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="I96" s="40">
-        <f>SUM(C96:H96)</f>
-        <v>18.440719999999999</v>
-      </c>
-      <c r="J96" s="40">
-        <f>I96+G$9</f>
-        <v>61.640719999999995</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A97" s="15"/>
-      <c r="B97" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C97" s="42"/>
-      <c r="D97" s="47">
-        <f>C97</f>
-        <v>0</v>
-      </c>
-      <c r="E97" s="47">
-        <f>D97</f>
-        <v>0</v>
-      </c>
-      <c r="F97" s="47">
-        <f>E97</f>
-        <v>0</v>
-      </c>
-      <c r="G97" s="42"/>
-      <c r="H97" s="42"/>
-      <c r="I97" s="56" t="s">
-        <v>84</v>
-      </c>
-      <c r="J97" s="87"/>
-    </row>
-    <row r="98" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="15"/>
-      <c r="B98" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="C98" s="38">
-        <f t="shared" ref="C98:H98" si="39">C97*(1+C97/3)*0.6</f>
-        <v>0</v>
-      </c>
-      <c r="D98" s="38">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="E98" s="38">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="F98" s="38">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="G98" s="38">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="H98" s="38">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="I98" s="40">
-        <f>SUM(C98:H98)</f>
-        <v>0</v>
-      </c>
-      <c r="J98" s="39">
-        <f>J97*(1+J97/3)*0.6*$C$7+I98</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A99" s="15"/>
-      <c r="B99" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C99" s="88"/>
-      <c r="D99" s="47">
-        <f>C99</f>
-        <v>0</v>
-      </c>
-      <c r="E99" s="47">
-        <f>D99</f>
-        <v>0</v>
-      </c>
-      <c r="F99" s="47">
-        <f>E99</f>
-        <v>0</v>
-      </c>
-      <c r="G99" s="88"/>
-      <c r="H99" s="88"/>
-      <c r="I99" s="56" t="s">
-        <v>84</v>
-      </c>
-      <c r="J99" s="89"/>
-    </row>
-    <row r="100" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="15"/>
-      <c r="B100" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="C100" s="38">
-        <f t="shared" ref="C100:H100" si="40">C99*(1+C99/3)*0.6</f>
-        <v>0</v>
-      </c>
-      <c r="D100" s="38">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="E100" s="38">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="F100" s="38">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="G100" s="38">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="H100" s="38">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="I100" s="38">
-        <f>SUM(C100:H100)</f>
-        <v>0</v>
-      </c>
-      <c r="J100" s="39">
-        <f>J99*(1+J99/3)*0.6*$C$7+I100</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A101" s="15"/>
-      <c r="B101" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="C101" s="42"/>
-      <c r="D101" s="47">
-        <f>C101</f>
-        <v>0</v>
-      </c>
-      <c r="E101" s="47">
-        <f>D101</f>
-        <v>0</v>
-      </c>
-      <c r="F101" s="47">
-        <f>E101</f>
-        <v>0</v>
-      </c>
-      <c r="G101" s="42"/>
-      <c r="H101" s="42"/>
-      <c r="I101" s="56" t="s">
-        <v>84</v>
-      </c>
-      <c r="J101" s="87"/>
-    </row>
-    <row r="102" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="15"/>
-      <c r="B102" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="C102" s="38">
-        <f t="shared" ref="C102:H102" si="41">C101*(1+C101/3)*0.6</f>
-        <v>0</v>
-      </c>
-      <c r="D102" s="38">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="E102" s="38">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="F102" s="38">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="G102" s="38">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="H102" s="38">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="I102" s="40">
-        <f>SUM(C102:H102)</f>
-        <v>0</v>
-      </c>
-      <c r="J102" s="39">
-        <f>J101*(1+J101/3)*0.6*$C$7+I102</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B104" s="9" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="7"/>
-    </row>
-    <row r="108" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I108" s="14"/>
-      <c r="J108" s="14"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="J36">
-    <cfRule type="cellIs" dxfId="92" priority="30" stopIfTrue="1" operator="lessThan">
-      <formula>65</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="31" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>65</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J44">
-    <cfRule type="cellIs" dxfId="90" priority="28" stopIfTrue="1" operator="lessThan">
-      <formula>75</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="29" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>75</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J46">
-    <cfRule type="cellIs" dxfId="88" priority="24" stopIfTrue="1" operator="greaterThan">
-      <formula>95</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="25" stopIfTrue="1" operator="lessThan">
-      <formula>85</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="86" priority="26" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>90</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="27" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>85</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J62">
-    <cfRule type="cellIs" dxfId="84" priority="21" stopIfTrue="1" operator="lessThanOrEqual">
-      <formula>80</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="22" stopIfTrue="1" operator="lessThanOrEqual">
-      <formula>90</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="23" stopIfTrue="1" operator="greaterThan">
-      <formula>90</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J70">
-    <cfRule type="cellIs" dxfId="81" priority="18" stopIfTrue="1" operator="lessThanOrEqual">
-      <formula>65</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="19" stopIfTrue="1" operator="lessThanOrEqual">
-      <formula>75</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="20" stopIfTrue="1" operator="greaterThan">
-      <formula>75</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J76">
-    <cfRule type="cellIs" dxfId="78" priority="15" stopIfTrue="1" operator="lessThanOrEqual">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="77" priority="16" stopIfTrue="1" operator="lessThanOrEqual">
-      <formula>75</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="17" stopIfTrue="1" operator="greaterThan">
-      <formula>75</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J66">
-    <cfRule type="cellIs" dxfId="75" priority="12" stopIfTrue="1" operator="lessThanOrEqual">
-      <formula>65</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="13" stopIfTrue="1" operator="lessThanOrEqual">
-      <formula>75</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="14" stopIfTrue="1" operator="greaterThan">
-      <formula>75</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J82">
-    <cfRule type="cellIs" dxfId="72" priority="9" stopIfTrue="1" operator="lessThanOrEqual">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="10" stopIfTrue="1" operator="lessThanOrEqual">
-      <formula>75</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="11" stopIfTrue="1" operator="greaterThan">
-      <formula>75</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J52">
-    <cfRule type="cellIs" dxfId="69" priority="7" stopIfTrue="1" operator="lessThan">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>60</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C24:F26">
-    <cfRule type="expression" dxfId="67" priority="4">
-      <formula>C$24+C$25+C$26&gt;1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="66" priority="5">
-      <formula>C$24+C$25+C$26&lt;1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="65" priority="6">
-      <formula>(C$24+C$25+C$26)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J40">
-    <cfRule type="cellIs" dxfId="64" priority="1" stopIfTrue="1" operator="lessThan">
-      <formula>90</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="2" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>95</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="3" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>90</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L108"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="1" width="2.28515625" style="9" customWidth="1"/>
-    <col min="2" max="2" width="21" style="9" customWidth="1"/>
-    <col min="3" max="8" width="9.28515625" style="9" customWidth="1"/>
-    <col min="9" max="10" width="10.140625" style="9" customWidth="1"/>
-    <col min="11" max="11" width="17" style="9" customWidth="1"/>
-    <col min="12" max="12" width="15.7109375" style="9" customWidth="1"/>
-    <col min="13" max="16384" width="11.42578125" style="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="E1" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-    </row>
-    <row r="3" spans="1:10" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="J3" s="70"/>
-    </row>
-    <row r="4" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-    </row>
-    <row r="5" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="13"/>
-      <c r="G5" s="77" t="s">
-        <v>7</v>
-      </c>
-      <c r="H5" s="53"/>
-      <c r="I5" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="J5" s="75"/>
-    </row>
-    <row r="6" spans="1:10" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="A6" s="15"/>
-      <c r="B6" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="17">
-        <v>1.8</v>
-      </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="F6" s="18"/>
-      <c r="G6" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="H6" s="53"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="74" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A7" s="15"/>
-      <c r="B7" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="17">
-        <v>25</v>
-      </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="19">
-        <f>C6*C7*(1+C6/10)/1.2</f>
-        <v>44.25</v>
-      </c>
-      <c r="F7" s="19"/>
-      <c r="G7" s="79">
-        <f>C6*C7*(1+C6/3)*0.6</f>
-        <v>43.199999999999996</v>
-      </c>
-      <c r="H7" s="53"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-    </row>
-    <row r="8" spans="1:10" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="A8" s="15"/>
-      <c r="B8" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="19">
-        <f>C6/2*C8*(1+C6/2/10)/1.2</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="19"/>
-      <c r="G8" s="79">
-        <f>C6/2*C8*(1+C6/2/3)*0.6</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="53"/>
-      <c r="I8" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="J8" s="71" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A9" s="20"/>
-      <c r="B9" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="22">
-        <f>C6*(C7+C8)</f>
-        <v>45</v>
-      </c>
-      <c r="D9" s="23"/>
-      <c r="E9" s="22">
-        <f>E7+E8</f>
-        <v>44.25</v>
-      </c>
-      <c r="F9" s="24"/>
-      <c r="G9" s="83">
-        <f>G7+G8</f>
-        <v>43.199999999999996</v>
-      </c>
-      <c r="H9" s="53"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-    </row>
-    <row r="10" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="15"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="80"/>
-      <c r="I10" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="J10" s="71"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A11" s="15"/>
-      <c r="B11" s="76" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" s="17"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="80"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="90"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A12" s="20"/>
-      <c r="B12" s="81" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" s="17"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="82"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="90"/>
-    </row>
-    <row r="13" spans="1:10" ht="5.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I13" s="10"/>
-      <c r="J13" s="90"/>
-    </row>
-    <row r="14" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="10"/>
-      <c r="B15" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="27">
-        <v>46265</v>
-      </c>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
-      <c r="J15" s="73" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="F16" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-    </row>
-    <row r="17" spans="1:10" s="14" customFormat="1" ht="3.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="29"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="53"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="53"/>
-    </row>
-    <row r="18" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="C18" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="D18" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="J18" s="25" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="9.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B19" s="60" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" s="68"/>
-      <c r="D19" s="68" t="s">
-        <v>40</v>
-      </c>
-      <c r="E19" s="68" t="s">
-        <v>40</v>
-      </c>
-      <c r="F19" s="68" t="s">
-        <v>41</v>
-      </c>
-      <c r="G19" s="68"/>
-      <c r="H19" s="68"/>
-      <c r="I19" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="J19" s="25" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="9.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="72"/>
-      <c r="D20" s="72"/>
-      <c r="E20" s="72"/>
-      <c r="F20" s="72"/>
-      <c r="G20" s="72"/>
-      <c r="H20" s="72"/>
-      <c r="I20" s="25"/>
-      <c r="J20" s="25"/>
-    </row>
-    <row r="21" spans="1:10" ht="9.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="43" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" s="69"/>
-      <c r="D21" s="69"/>
-      <c r="E21" s="69"/>
-      <c r="F21" s="69"/>
-      <c r="G21" s="69"/>
-      <c r="H21" s="69"/>
-      <c r="I21" s="65" t="s">
-        <v>21</v>
-      </c>
-      <c r="J21" s="65" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="9.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="49"/>
-      <c r="J22" s="49"/>
-    </row>
-    <row r="23" spans="1:10" ht="9.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="32"/>
-      <c r="B23" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33">
-        <f>C23</f>
-        <v>0</v>
-      </c>
-      <c r="E23" s="33">
-        <f>D23</f>
-        <v>0</v>
-      </c>
-      <c r="F23" s="33">
-        <f>E23</f>
-        <v>0</v>
-      </c>
-      <c r="G23" s="33"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="34">
-        <f>SUM(C23:H23)</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="61"/>
-    </row>
-    <row r="24" spans="1:10" ht="9.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="15"/>
-      <c r="B24" s="93" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" s="96"/>
-      <c r="D24" s="96">
-        <f>C24</f>
-        <v>0</v>
-      </c>
-      <c r="E24" s="96"/>
-      <c r="F24" s="96"/>
-      <c r="G24" s="92"/>
-      <c r="H24" s="92"/>
-      <c r="I24" s="91"/>
-      <c r="J24" s="58"/>
-    </row>
-    <row r="25" spans="1:10" ht="9.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="15"/>
-      <c r="B25" s="93" t="s">
-        <v>82</v>
-      </c>
-      <c r="C25" s="96"/>
-      <c r="D25" s="96">
-        <f>C25</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="96"/>
-      <c r="F25" s="96"/>
-      <c r="G25" s="92"/>
-      <c r="H25" s="92"/>
-      <c r="I25" s="91"/>
-      <c r="J25" s="58"/>
-    </row>
-    <row r="26" spans="1:10" ht="9.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="15"/>
-      <c r="B26" s="93" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" s="96"/>
-      <c r="D26" s="96">
-        <f>C26</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="96"/>
-      <c r="F26" s="96"/>
-      <c r="G26" s="92"/>
-      <c r="H26" s="92"/>
-      <c r="I26" s="91"/>
-      <c r="J26" s="58"/>
-    </row>
-    <row r="27" spans="1:10" s="14" customFormat="1" ht="3.95" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="55"/>
-      <c r="B27" s="53"/>
-      <c r="C27" s="56"/>
-      <c r="D27" s="56"/>
-      <c r="E27" s="56"/>
-      <c r="F27" s="56"/>
-      <c r="G27" s="56"/>
-      <c r="H27" s="56"/>
-      <c r="I27" s="57"/>
-      <c r="J27" s="58"/>
-    </row>
-    <row r="28" spans="1:10" ht="9.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="15"/>
-      <c r="B28" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36">
-        <f>C28</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="36">
-        <f>D28</f>
-        <v>0</v>
-      </c>
-      <c r="F28" s="36">
-        <f>E28</f>
-        <v>0</v>
-      </c>
-      <c r="G28" s="36"/>
-      <c r="H28" s="36"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="58"/>
-    </row>
-    <row r="29" spans="1:10" ht="9.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="15"/>
-      <c r="B29" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="C29" s="38">
-        <f t="shared" ref="C29:H29" si="0">C28*(1+C28/10)/1.2</f>
-        <v>0</v>
-      </c>
-      <c r="D29" s="38">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E29" s="38">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F29" s="38">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G29" s="38">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H29" s="38">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I29" s="40">
-        <f>SUM(C29:H29)</f>
-        <v>0</v>
-      </c>
-      <c r="J29" s="39">
-        <f>I29+E9</f>
-        <v>44.25</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" s="14" customFormat="1" ht="3.95" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="55"/>
-      <c r="B30" s="53"/>
-      <c r="C30" s="56"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="56"/>
-      <c r="G30" s="56"/>
-      <c r="H30" s="56"/>
-      <c r="I30" s="56"/>
-      <c r="J30" s="59"/>
-    </row>
-    <row r="31" spans="1:10" ht="9.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="15"/>
-      <c r="B31" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="42" t="s">
-        <v>85</v>
-      </c>
-      <c r="D31" s="42" t="str">
-        <f>C31</f>
-        <v>x</v>
-      </c>
-      <c r="E31" s="42" t="str">
-        <f>D31</f>
-        <v>x</v>
-      </c>
-      <c r="F31" s="42" t="str">
-        <f>E31</f>
-        <v>x</v>
-      </c>
-      <c r="G31" s="42"/>
-      <c r="H31" s="42"/>
-      <c r="I31" s="63"/>
-      <c r="J31" s="64"/>
-    </row>
-    <row r="32" spans="1:10" ht="9.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="15"/>
-      <c r="B32" s="37" t="s">
-        <v>71</v>
-      </c>
-      <c r="C32" s="38" t="e">
-        <f t="shared" ref="C32:H32" si="1">C31*(1+C31/10)/1.2</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D32" s="38" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E32" s="38" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F32" s="38" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G32" s="38">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H32" s="38">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I32" s="40" t="e">
-        <f>SUM(C32:H32)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J32" s="39" t="e">
-        <f>I32+E9</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="9.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="15"/>
-      <c r="B33" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="C33" s="42" t="s">
-        <v>85</v>
-      </c>
-      <c r="D33" s="42" t="str">
-        <f>C33</f>
-        <v>x</v>
-      </c>
-      <c r="E33" s="42" t="str">
-        <f>D33</f>
-        <v>x</v>
-      </c>
-      <c r="F33" s="42" t="str">
-        <f>E33</f>
-        <v>x</v>
-      </c>
-      <c r="G33" s="42"/>
-      <c r="H33" s="42"/>
-      <c r="I33" s="56"/>
-      <c r="J33" s="58"/>
-    </row>
-    <row r="34" spans="1:12" ht="9.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="15"/>
-      <c r="B34" s="37" t="s">
-        <v>72</v>
-      </c>
-      <c r="C34" s="38" t="e">
-        <f t="shared" ref="C34:H34" si="2">C33*(1+C33/10)/1.2</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D34" s="38" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E34" s="38" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F34" s="38" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G34" s="38">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H34" s="38">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I34" s="40" t="e">
-        <f>SUM(C34:H34)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J34" s="39" t="e">
-        <f>I34+E9</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="9.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="15"/>
-      <c r="B35" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="C35" s="44" t="s">
-        <v>85</v>
-      </c>
-      <c r="D35" s="44" t="e">
-        <f>(D31+D33)/2</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E35" s="44" t="e">
-        <f>(E31+E33)/2</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F35" s="44" t="e">
-        <f>(F31+F33)/2</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G35" s="44">
-        <f>(G31+G33)/2</f>
-        <v>0</v>
-      </c>
-      <c r="H35" s="44">
-        <f>(H31+H33)/2</f>
-        <v>0</v>
-      </c>
-      <c r="I35" s="56"/>
-      <c r="J35" s="58"/>
-    </row>
-    <row r="36" spans="1:12" ht="9.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="45"/>
-      <c r="B36" s="37" t="s">
-        <v>73</v>
-      </c>
-      <c r="C36" s="38" t="e">
-        <f t="shared" ref="C36:H36" si="3">C35*(1+C35/10)/1.2</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D36" s="38" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E36" s="38" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F36" s="38" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G36" s="38">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H36" s="38">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I36" s="40" t="e">
-        <f>SUM(C36:H36)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J36" s="39" t="e">
-        <f>I36+E9</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="16"/>
-      <c r="B37" s="16"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="54"/>
-      <c r="J37" s="30"/>
-    </row>
-    <row r="38" spans="1:12" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="A38" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B38" s="46"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17">
-        <v>0</v>
-      </c>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="36"/>
-      <c r="H38" s="36"/>
-      <c r="I38" s="66">
-        <f>AVERAGE(C38:H38)</f>
-        <v>0</v>
-      </c>
-      <c r="J38" s="67">
-        <f>STDEVP(C38:H38)</f>
-        <v>0</v>
-      </c>
-      <c r="K38" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="L38" s="25" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="15"/>
-      <c r="B39" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="C39" s="47">
-        <v>12.14</v>
-      </c>
-      <c r="D39" s="47">
-        <f>C39</f>
-        <v>12.14</v>
-      </c>
-      <c r="E39" s="47">
-        <f t="shared" ref="E39:F39" si="4">D39</f>
-        <v>12.14</v>
-      </c>
-      <c r="F39" s="47">
-        <f t="shared" si="4"/>
-        <v>12.14</v>
-      </c>
-      <c r="G39" s="42"/>
-      <c r="H39" s="42"/>
-      <c r="I39" s="56"/>
-      <c r="J39" s="58"/>
-    </row>
-    <row r="40" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="15"/>
-      <c r="B40" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="C40" s="38">
-        <f t="shared" ref="C40:H40" si="5">C39*(1+C39/10)/1.2</f>
-        <v>22.398300000000003</v>
-      </c>
-      <c r="D40" s="38">
-        <f t="shared" si="5"/>
-        <v>22.398300000000003</v>
-      </c>
-      <c r="E40" s="38">
-        <f t="shared" si="5"/>
-        <v>22.398300000000003</v>
-      </c>
-      <c r="F40" s="38">
-        <f t="shared" si="5"/>
-        <v>22.398300000000003</v>
-      </c>
-      <c r="G40" s="38">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H40" s="38">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="I40" s="40">
-        <f>SUM(C40:H40)</f>
-        <v>89.59320000000001</v>
-      </c>
-      <c r="J40" s="39">
-        <f>I40+E$9</f>
-        <v>133.84320000000002</v>
-      </c>
-      <c r="K40" s="49" t="s">
-        <v>93</v>
-      </c>
-      <c r="L40" s="49" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" s="14" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C41" s="48"/>
-      <c r="D41" s="48"/>
-      <c r="E41" s="48"/>
-      <c r="F41" s="48"/>
-      <c r="G41" s="48"/>
-      <c r="H41" s="48"/>
-      <c r="I41" s="48"/>
-      <c r="J41" s="48"/>
-      <c r="K41" s="49"/>
-      <c r="L41" s="49"/>
-    </row>
-    <row r="42" spans="1:12" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="A42" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B42" s="46"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="33"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="36"/>
-      <c r="H42" s="36"/>
-      <c r="I42" s="66" t="e">
-        <f>AVERAGE(C42:H42)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J42" s="67" t="e">
-        <f>STDEVP(C42:H42)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K42" s="97"/>
-      <c r="L42" s="97"/>
-    </row>
-    <row r="43" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="15"/>
-      <c r="B43" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="C43" s="47">
-        <v>6.4</v>
-      </c>
-      <c r="D43" s="47">
-        <f>C43</f>
-        <v>6.4</v>
-      </c>
-      <c r="E43" s="47">
-        <f t="shared" ref="E43:F43" si="6">D43</f>
-        <v>6.4</v>
-      </c>
-      <c r="F43" s="47">
-        <f t="shared" si="6"/>
-        <v>6.4</v>
-      </c>
-      <c r="G43" s="42"/>
-      <c r="H43" s="42"/>
-      <c r="I43" s="56"/>
-      <c r="J43" s="58"/>
-      <c r="K43" s="97"/>
-      <c r="L43" s="97"/>
-    </row>
-    <row r="44" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="15"/>
-      <c r="B44" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="C44" s="38">
-        <f t="shared" ref="C44:H44" si="7">C43*(1+C43/10)/1.2</f>
-        <v>8.7466666666666697</v>
-      </c>
-      <c r="D44" s="38">
-        <f t="shared" si="7"/>
-        <v>8.7466666666666697</v>
-      </c>
-      <c r="E44" s="38">
-        <f t="shared" si="7"/>
-        <v>8.7466666666666697</v>
-      </c>
-      <c r="F44" s="38">
-        <f t="shared" si="7"/>
-        <v>8.7466666666666697</v>
-      </c>
-      <c r="G44" s="38">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="H44" s="38">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I44" s="40">
-        <f>SUM(C44:H44)</f>
-        <v>34.986666666666679</v>
-      </c>
-      <c r="J44" s="39">
-        <f>I44+E$9</f>
-        <v>79.236666666666679</v>
-      </c>
-      <c r="K44" s="49" t="s">
-        <v>95</v>
-      </c>
-      <c r="L44" s="49" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="15"/>
-      <c r="B45" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="C45" s="47">
-        <v>7.43</v>
-      </c>
-      <c r="D45" s="47">
-        <f>C45</f>
-        <v>7.43</v>
-      </c>
-      <c r="E45" s="47">
-        <f t="shared" ref="E45:F45" si="8">D45</f>
-        <v>7.43</v>
-      </c>
-      <c r="F45" s="47">
-        <f t="shared" si="8"/>
-        <v>7.43</v>
-      </c>
-      <c r="G45" s="42"/>
-      <c r="H45" s="42"/>
-      <c r="I45" s="56"/>
-      <c r="J45" s="58"/>
-      <c r="K45" s="97"/>
-      <c r="L45" s="97"/>
-    </row>
-    <row r="46" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="15"/>
-      <c r="B46" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="C46" s="38">
-        <f t="shared" ref="C46:H46" si="9">C45*(1+C45/10)/1.2</f>
-        <v>10.792074999999999</v>
-      </c>
-      <c r="D46" s="38">
-        <f t="shared" si="9"/>
-        <v>10.792074999999999</v>
-      </c>
-      <c r="E46" s="38">
-        <f t="shared" si="9"/>
-        <v>10.792074999999999</v>
-      </c>
-      <c r="F46" s="38">
-        <f t="shared" si="9"/>
-        <v>10.792074999999999</v>
-      </c>
-      <c r="G46" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H46" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="I46" s="40">
-        <f>SUM(C46:H46)</f>
-        <v>43.168299999999995</v>
-      </c>
-      <c r="J46" s="39">
-        <f>I46+E$9</f>
-        <v>87.418299999999988</v>
-      </c>
-      <c r="K46" s="97" t="s">
-        <v>91</v>
-      </c>
-      <c r="L46" s="49" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="15"/>
-      <c r="B47" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="C47" s="47">
-        <v>10.64</v>
-      </c>
-      <c r="D47" s="47">
-        <f>C47</f>
-        <v>10.64</v>
-      </c>
-      <c r="E47" s="47">
-        <f t="shared" ref="E47:F47" si="10">D47</f>
-        <v>10.64</v>
-      </c>
-      <c r="F47" s="47">
-        <f t="shared" si="10"/>
-        <v>10.64</v>
-      </c>
-      <c r="G47" s="42"/>
-      <c r="H47" s="42"/>
-      <c r="I47" s="56"/>
-      <c r="J47" s="58"/>
-    </row>
-    <row r="48" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="15"/>
-      <c r="B48" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="C48" s="38">
-        <f t="shared" ref="C48:H48" si="11">C47*(1+C47/10)/1.2</f>
-        <v>18.300800000000002</v>
-      </c>
-      <c r="D48" s="38">
-        <f t="shared" si="11"/>
-        <v>18.300800000000002</v>
-      </c>
-      <c r="E48" s="38">
-        <f t="shared" si="11"/>
-        <v>18.300800000000002</v>
-      </c>
-      <c r="F48" s="38">
-        <f t="shared" si="11"/>
-        <v>18.300800000000002</v>
-      </c>
-      <c r="G48" s="38">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H48" s="38">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I48" s="40">
-        <f>SUM(C48:H48)</f>
-        <v>73.20320000000001</v>
-      </c>
-      <c r="J48" s="39">
-        <f>I48+E9</f>
-        <v>117.45320000000001</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="16"/>
-      <c r="B49" s="16"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="19"/>
-      <c r="G49" s="19"/>
-      <c r="H49" s="19"/>
-      <c r="I49" s="54"/>
-      <c r="J49" s="30"/>
-    </row>
-    <row r="50" spans="1:12" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="A50" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B50" s="46"/>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17">
-        <v>0</v>
-      </c>
-      <c r="E50" s="17"/>
-      <c r="F50" s="17"/>
-      <c r="G50" s="36"/>
-      <c r="H50" s="36"/>
-      <c r="I50" s="66">
-        <f>AVERAGE(C50:H50)</f>
-        <v>0</v>
-      </c>
-      <c r="J50" s="67">
-        <f>STDEVP(C50:H50)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="15"/>
-      <c r="B51" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="C51" s="47">
-        <v>3.3</v>
-      </c>
-      <c r="D51" s="47">
-        <f>C51</f>
-        <v>3.3</v>
-      </c>
-      <c r="E51" s="47">
-        <f t="shared" ref="E51" si="12">D51</f>
-        <v>3.3</v>
-      </c>
-      <c r="F51" s="47">
-        <f>E51</f>
-        <v>3.3</v>
-      </c>
-      <c r="G51" s="42"/>
-      <c r="H51" s="42"/>
-      <c r="I51" s="56"/>
-      <c r="J51" s="58"/>
-    </row>
-    <row r="52" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="15"/>
-      <c r="B52" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="C52" s="38">
-        <f t="shared" ref="C52:H52" si="13">C51*(1+C51/10)/1.2</f>
-        <v>3.6575000000000002</v>
-      </c>
-      <c r="D52" s="38">
-        <f t="shared" si="13"/>
-        <v>3.6575000000000002</v>
-      </c>
-      <c r="E52" s="38">
-        <f t="shared" si="13"/>
-        <v>3.6575000000000002</v>
-      </c>
-      <c r="F52" s="38">
-        <f t="shared" si="13"/>
-        <v>3.6575000000000002</v>
-      </c>
-      <c r="G52" s="38">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="H52" s="38">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="I52" s="40">
-        <f>SUM(C52:H52)</f>
-        <v>14.63</v>
-      </c>
-      <c r="J52" s="39">
-        <f>I52+E$9</f>
-        <v>58.88</v>
-      </c>
-      <c r="K52" s="49" t="s">
-        <v>96</v>
-      </c>
-      <c r="L52" s="49" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="15"/>
-      <c r="B53" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="C53" s="47">
-        <v>4.38</v>
-      </c>
-      <c r="D53" s="47">
-        <f>C53</f>
-        <v>4.38</v>
-      </c>
-      <c r="E53" s="47">
-        <f t="shared" ref="E53:F53" si="14">D53</f>
-        <v>4.38</v>
-      </c>
-      <c r="F53" s="47">
-        <f t="shared" si="14"/>
-        <v>4.38</v>
-      </c>
-      <c r="G53" s="42"/>
-      <c r="H53" s="42"/>
-      <c r="I53" s="56"/>
-      <c r="J53" s="58"/>
-      <c r="K53" s="97"/>
-      <c r="L53" s="97"/>
-    </row>
-    <row r="54" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="15"/>
-      <c r="B54" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="C54" s="38">
-        <f t="shared" ref="C54:H54" si="15">C53*(1+C53/10)/1.2</f>
-        <v>5.2486999999999995</v>
-      </c>
-      <c r="D54" s="38">
-        <f t="shared" si="15"/>
-        <v>5.2486999999999995</v>
-      </c>
-      <c r="E54" s="38">
-        <f t="shared" si="15"/>
-        <v>5.2486999999999995</v>
-      </c>
-      <c r="F54" s="38">
-        <f t="shared" si="15"/>
-        <v>5.2486999999999995</v>
-      </c>
-      <c r="G54" s="38">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="H54" s="38">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="I54" s="40">
-        <f>SUM(C54:H54)</f>
-        <v>20.994799999999998</v>
-      </c>
-      <c r="J54" s="39">
-        <f>I54+E$9</f>
-        <v>65.244799999999998</v>
-      </c>
-      <c r="K54" s="97"/>
-      <c r="L54" s="97"/>
-    </row>
-    <row r="55" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="K55" s="97"/>
-      <c r="L55" s="97"/>
-    </row>
-    <row r="56" spans="1:12" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="A56" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B56" s="46"/>
-      <c r="C56" s="36"/>
-      <c r="D56" s="36">
-        <f>C56</f>
-        <v>0</v>
-      </c>
-      <c r="E56" s="36"/>
-      <c r="F56" s="36"/>
-      <c r="G56" s="36"/>
-      <c r="H56" s="36"/>
-      <c r="I56" s="66">
-        <f>AVERAGE(C56:H56)</f>
-        <v>0</v>
-      </c>
-      <c r="J56" s="67">
-        <f>STDEVP(C56:H56)</f>
-        <v>0</v>
-      </c>
-      <c r="K56" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="L56" s="25" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A57" s="15"/>
-      <c r="B57" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="C57" s="47"/>
-      <c r="D57" s="47"/>
-      <c r="E57" s="47"/>
-      <c r="F57" s="47"/>
-      <c r="G57" s="42"/>
-      <c r="H57" s="42"/>
-      <c r="I57" s="56"/>
-      <c r="J57" s="58"/>
-      <c r="K57" s="97"/>
-      <c r="L57" s="97"/>
-    </row>
-    <row r="58" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="15"/>
-      <c r="B58" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="C58" s="38">
-        <f t="shared" ref="C58:H58" si="16">C57*(1+C57/3)*0.6</f>
-        <v>0</v>
-      </c>
-      <c r="D58" s="38">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="E58" s="38">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="F58" s="38">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="G58" s="38">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="H58" s="38">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I58" s="40">
-        <f>SUM(C58:H58)</f>
-        <v>0</v>
-      </c>
-      <c r="J58" s="39">
-        <f>I58+G9</f>
-        <v>43.199999999999996</v>
-      </c>
-      <c r="K58" s="97"/>
-      <c r="L58" s="97"/>
-    </row>
-    <row r="59" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="15"/>
-      <c r="B59" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="C59" s="47">
-        <v>5.45</v>
-      </c>
-      <c r="D59" s="47">
-        <f>C59</f>
-        <v>5.45</v>
-      </c>
-      <c r="E59" s="47">
-        <f t="shared" ref="E59:F59" si="17">D59</f>
-        <v>5.45</v>
-      </c>
-      <c r="F59" s="47">
-        <f t="shared" si="17"/>
-        <v>5.45</v>
-      </c>
-      <c r="G59" s="42"/>
-      <c r="H59" s="42"/>
-      <c r="I59" s="56"/>
-      <c r="J59" s="58"/>
-      <c r="K59" s="97"/>
-      <c r="L59" s="97"/>
-    </row>
-    <row r="60" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="15"/>
-      <c r="B60" s="37" t="s">
-        <v>64</v>
-      </c>
-      <c r="C60" s="38">
-        <f t="shared" ref="C60:H60" si="18">C59*(1+C59/3)*0.6</f>
-        <v>9.2104999999999997</v>
-      </c>
-      <c r="D60" s="38">
-        <f t="shared" si="18"/>
-        <v>9.2104999999999997</v>
-      </c>
-      <c r="E60" s="38">
-        <f t="shared" si="18"/>
-        <v>9.2104999999999997</v>
-      </c>
-      <c r="F60" s="38">
-        <f t="shared" si="18"/>
-        <v>9.2104999999999997</v>
-      </c>
-      <c r="G60" s="38">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="H60" s="38">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="I60" s="40">
-        <f>SUM(C60:H60)</f>
-        <v>36.841999999999999</v>
-      </c>
-      <c r="J60" s="40">
-        <f>I60+G9</f>
-        <v>80.042000000000002</v>
-      </c>
-      <c r="K60" s="97"/>
-      <c r="L60" s="97"/>
-    </row>
-    <row r="61" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="15"/>
-      <c r="B61" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="C61" s="47">
-        <v>4.41</v>
-      </c>
-      <c r="D61" s="47">
-        <f>C61</f>
-        <v>4.41</v>
-      </c>
-      <c r="E61" s="47">
-        <f t="shared" ref="E61:F61" si="19">D61</f>
-        <v>4.41</v>
-      </c>
-      <c r="F61" s="47">
-        <f t="shared" si="19"/>
-        <v>4.41</v>
-      </c>
-      <c r="G61" s="42"/>
-      <c r="H61" s="42"/>
-      <c r="I61" s="56"/>
-      <c r="J61" s="58"/>
-      <c r="K61" s="97"/>
-      <c r="L61" s="97"/>
-    </row>
-    <row r="62" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="20"/>
-      <c r="B62" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="C62" s="38">
-        <f t="shared" ref="C62:H62" si="20">C61*(1+C61/3)*0.6</f>
-        <v>6.5356199999999998</v>
-      </c>
-      <c r="D62" s="38">
-        <f t="shared" si="20"/>
-        <v>6.5356199999999998</v>
-      </c>
-      <c r="E62" s="38">
-        <f t="shared" si="20"/>
-        <v>6.5356199999999998</v>
-      </c>
-      <c r="F62" s="38">
-        <f t="shared" si="20"/>
-        <v>6.5356199999999998</v>
-      </c>
-      <c r="G62" s="38">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="H62" s="38">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="I62" s="40">
-        <f>SUM(C62:H62)</f>
-        <v>26.142479999999999</v>
-      </c>
-      <c r="J62" s="39">
-        <f>I62+G9</f>
-        <v>69.342479999999995</v>
-      </c>
-      <c r="K62" s="49" t="s">
-        <v>97</v>
-      </c>
-      <c r="L62" s="49" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" s="14" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C63" s="48"/>
-      <c r="D63" s="48"/>
-      <c r="E63" s="48"/>
-      <c r="F63" s="48"/>
-      <c r="G63" s="48"/>
-      <c r="H63" s="48"/>
-      <c r="I63" s="48"/>
-      <c r="J63" s="48"/>
-      <c r="K63" s="49"/>
-      <c r="L63" s="49"/>
-    </row>
-    <row r="64" spans="1:12" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="A64" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B64" s="46"/>
-      <c r="C64" s="36"/>
-      <c r="D64" s="36">
-        <f>C64</f>
-        <v>0</v>
-      </c>
-      <c r="E64" s="36"/>
-      <c r="F64" s="36"/>
-      <c r="G64" s="36"/>
-      <c r="H64" s="36"/>
-      <c r="I64" s="66">
-        <f>AVERAGE(C64:H64)</f>
-        <v>0</v>
-      </c>
-      <c r="J64" s="67">
-        <f>STDEVP(C64:H64)</f>
-        <v>0</v>
-      </c>
-      <c r="K64" s="97"/>
-      <c r="L64" s="97"/>
-    </row>
-    <row r="65" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A65" s="15"/>
-      <c r="B65" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="C65" s="47">
-        <v>4.8600000000000003</v>
-      </c>
-      <c r="D65" s="47">
-        <f>C65</f>
-        <v>4.8600000000000003</v>
-      </c>
-      <c r="E65" s="47">
-        <f t="shared" ref="E65:F65" si="21">D65</f>
-        <v>4.8600000000000003</v>
-      </c>
-      <c r="F65" s="47">
-        <f t="shared" si="21"/>
-        <v>4.8600000000000003</v>
-      </c>
-      <c r="G65" s="42"/>
-      <c r="H65" s="42"/>
-      <c r="I65" s="56"/>
-      <c r="J65" s="58"/>
-      <c r="K65" s="97"/>
-      <c r="L65" s="97"/>
-    </row>
-    <row r="66" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="15"/>
-      <c r="B66" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="C66" s="38">
-        <f t="shared" ref="C66:H66" si="22">C65*(1+C65/3)*0.6</f>
-        <v>7.6399200000000009</v>
-      </c>
-      <c r="D66" s="38">
-        <f t="shared" si="22"/>
-        <v>7.6399200000000009</v>
-      </c>
-      <c r="E66" s="38">
-        <f t="shared" si="22"/>
-        <v>7.6399200000000009</v>
-      </c>
-      <c r="F66" s="38">
-        <f t="shared" si="22"/>
-        <v>7.6399200000000009</v>
-      </c>
-      <c r="G66" s="38">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="H66" s="38">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I66" s="40">
-        <f>SUM(C66:H66)</f>
-        <v>30.559680000000004</v>
-      </c>
-      <c r="J66" s="39">
-        <f>I66+G9</f>
-        <v>73.759680000000003</v>
-      </c>
-      <c r="K66" s="49" t="s">
         <v>99</v>
-      </c>
-      <c r="L66" s="49" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="15"/>
-      <c r="B67" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="C67" s="47">
-        <v>6.57</v>
-      </c>
-      <c r="D67" s="47">
-        <f>C67</f>
-        <v>6.57</v>
-      </c>
-      <c r="E67" s="47">
-        <f t="shared" ref="E67:F67" si="23">D67</f>
-        <v>6.57</v>
-      </c>
-      <c r="F67" s="47">
-        <f t="shared" si="23"/>
-        <v>6.57</v>
-      </c>
-      <c r="G67" s="42"/>
-      <c r="H67" s="42"/>
-      <c r="I67" s="56"/>
-      <c r="J67" s="58"/>
-      <c r="K67" s="97"/>
-      <c r="L67" s="97"/>
-    </row>
-    <row r="68" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="15"/>
-      <c r="B68" s="37" t="s">
-        <v>64</v>
-      </c>
-      <c r="C68" s="38">
-        <f t="shared" ref="C68:H68" si="24">C67*(1+C67/3)*0.6</f>
-        <v>12.57498</v>
-      </c>
-      <c r="D68" s="38">
-        <f t="shared" si="24"/>
-        <v>12.57498</v>
-      </c>
-      <c r="E68" s="38">
-        <f t="shared" si="24"/>
-        <v>12.57498</v>
-      </c>
-      <c r="F68" s="38">
-        <f t="shared" si="24"/>
-        <v>12.57498</v>
-      </c>
-      <c r="G68" s="38">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="H68" s="38">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="I68" s="40">
-        <f>SUM(C68:H68)</f>
-        <v>50.29992</v>
-      </c>
-      <c r="J68" s="40">
-        <f>I68+G9</f>
-        <v>93.499920000000003</v>
-      </c>
-      <c r="K68" s="97"/>
-      <c r="L68" s="97"/>
-    </row>
-    <row r="69" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="50"/>
-      <c r="B69" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="C69" s="47">
-        <v>3.99</v>
-      </c>
-      <c r="D69" s="47">
-        <f>C69</f>
-        <v>3.99</v>
-      </c>
-      <c r="E69" s="47">
-        <f t="shared" ref="E69:F69" si="25">D69</f>
-        <v>3.99</v>
-      </c>
-      <c r="F69" s="47">
-        <f t="shared" si="25"/>
-        <v>3.99</v>
-      </c>
-      <c r="G69" s="42"/>
-      <c r="H69" s="42"/>
-      <c r="I69" s="56"/>
-      <c r="J69" s="58"/>
-      <c r="K69" s="97"/>
-      <c r="L69" s="97"/>
-    </row>
-    <row r="70" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="20"/>
-      <c r="B70" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="C70" s="38">
-        <f t="shared" ref="C70:H70" si="26">C69*(1+C69/3)*0.6</f>
-        <v>5.5780200000000004</v>
-      </c>
-      <c r="D70" s="38">
-        <f t="shared" si="26"/>
-        <v>5.5780200000000004</v>
-      </c>
-      <c r="E70" s="38">
-        <f t="shared" si="26"/>
-        <v>5.5780200000000004</v>
-      </c>
-      <c r="F70" s="38">
-        <f t="shared" si="26"/>
-        <v>5.5780200000000004</v>
-      </c>
-      <c r="G70" s="38">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="H70" s="38">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="I70" s="40">
-        <f>SUM(C70:H70)</f>
-        <v>22.312080000000002</v>
-      </c>
-      <c r="J70" s="39">
-        <f>I70+G9</f>
-        <v>65.512079999999997</v>
-      </c>
-      <c r="K70" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="L70" s="49" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" s="14" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C71" s="48"/>
-      <c r="D71" s="48"/>
-      <c r="E71" s="48"/>
-      <c r="F71" s="48"/>
-      <c r="G71" s="48"/>
-      <c r="H71" s="48"/>
-      <c r="I71" s="48"/>
-      <c r="J71" s="48"/>
-      <c r="K71" s="49"/>
-      <c r="L71" s="49"/>
-    </row>
-    <row r="72" spans="1:12" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="A72" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B72" s="46"/>
-      <c r="C72" s="36"/>
-      <c r="D72" s="36">
-        <f>C72</f>
-        <v>0</v>
-      </c>
-      <c r="E72" s="36"/>
-      <c r="F72" s="36"/>
-      <c r="G72" s="36"/>
-      <c r="H72" s="36"/>
-      <c r="I72" s="66">
-        <f>AVERAGE(C72:H72)</f>
-        <v>0</v>
-      </c>
-      <c r="J72" s="67">
-        <f>STDEVP(C72:H72)</f>
-        <v>0</v>
-      </c>
-      <c r="K72" s="97"/>
-      <c r="L72" s="97"/>
-    </row>
-    <row r="73" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="15"/>
-      <c r="B73" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="C73" s="47">
-        <v>5.48</v>
-      </c>
-      <c r="D73" s="47">
-        <f>C73</f>
-        <v>5.48</v>
-      </c>
-      <c r="E73" s="47">
-        <f t="shared" ref="E73:F73" si="27">D73</f>
-        <v>5.48</v>
-      </c>
-      <c r="F73" s="47">
-        <f t="shared" si="27"/>
-        <v>5.48</v>
-      </c>
-      <c r="G73" s="42"/>
-      <c r="H73" s="42"/>
-      <c r="I73" s="56"/>
-      <c r="J73" s="58"/>
-      <c r="K73" s="97"/>
-      <c r="L73" s="97"/>
-    </row>
-    <row r="74" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="15"/>
-      <c r="B74" s="37" t="s">
-        <v>64</v>
-      </c>
-      <c r="C74" s="38">
-        <f t="shared" ref="C74:H74" si="28">C73*(1+C73/3)*0.6</f>
-        <v>9.294080000000001</v>
-      </c>
-      <c r="D74" s="38">
-        <f t="shared" si="28"/>
-        <v>9.294080000000001</v>
-      </c>
-      <c r="E74" s="38">
-        <f t="shared" si="28"/>
-        <v>9.294080000000001</v>
-      </c>
-      <c r="F74" s="38">
-        <f t="shared" si="28"/>
-        <v>9.294080000000001</v>
-      </c>
-      <c r="G74" s="38">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="H74" s="38">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="I74" s="40">
-        <f>SUM(C74:H74)</f>
-        <v>37.176320000000004</v>
-      </c>
-      <c r="J74" s="40">
-        <f>I74+G9</f>
-        <v>80.376319999999993</v>
-      </c>
-      <c r="K74" s="97"/>
-      <c r="L74" s="97"/>
-    </row>
-    <row r="75" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="15"/>
-      <c r="B75" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="C75" s="47">
-        <v>4.1500000000000004</v>
-      </c>
-      <c r="D75" s="47">
-        <f>C75</f>
-        <v>4.1500000000000004</v>
-      </c>
-      <c r="E75" s="47">
-        <f t="shared" ref="E75:F75" si="29">D75</f>
-        <v>4.1500000000000004</v>
-      </c>
-      <c r="F75" s="47">
-        <f t="shared" si="29"/>
-        <v>4.1500000000000004</v>
-      </c>
-      <c r="G75" s="42"/>
-      <c r="H75" s="42"/>
-      <c r="I75" s="56"/>
-      <c r="J75" s="58"/>
-      <c r="K75" s="97"/>
-      <c r="L75" s="97"/>
-    </row>
-    <row r="76" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="20"/>
-      <c r="B76" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="C76" s="38">
-        <f t="shared" ref="C76:H76" si="30">C75*(1+C75/3)*0.6</f>
-        <v>5.9345000000000017</v>
-      </c>
-      <c r="D76" s="38">
-        <f t="shared" si="30"/>
-        <v>5.9345000000000017</v>
-      </c>
-      <c r="E76" s="38">
-        <f t="shared" si="30"/>
-        <v>5.9345000000000017</v>
-      </c>
-      <c r="F76" s="38">
-        <f t="shared" si="30"/>
-        <v>5.9345000000000017</v>
-      </c>
-      <c r="G76" s="38">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="H76" s="38">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="I76" s="40">
-        <f>SUM(C76:H76)</f>
-        <v>23.738000000000007</v>
-      </c>
-      <c r="J76" s="39">
-        <f>I76+G9</f>
-        <v>66.938000000000002</v>
-      </c>
-      <c r="K76" s="49" t="s">
-        <v>101</v>
-      </c>
-      <c r="L76" s="49" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I77" s="14"/>
-      <c r="J77" s="14"/>
-      <c r="K77" s="97"/>
-      <c r="L77" s="97"/>
-    </row>
-    <row r="78" spans="1:12" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="A78" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B78" s="46"/>
-      <c r="C78" s="36"/>
-      <c r="D78" s="36">
-        <f>C78</f>
-        <v>0</v>
-      </c>
-      <c r="E78" s="36"/>
-      <c r="F78" s="36"/>
-      <c r="G78" s="36"/>
-      <c r="H78" s="36"/>
-      <c r="I78" s="66">
-        <f>AVERAGE(C78:H78)</f>
-        <v>0</v>
-      </c>
-      <c r="J78" s="67">
-        <f>STDEVP(C78:H78)</f>
-        <v>0</v>
-      </c>
-      <c r="K78" s="97"/>
-      <c r="L78" s="97"/>
-    </row>
-    <row r="79" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="15"/>
-      <c r="B79" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="C79" s="47">
-        <v>5.24</v>
-      </c>
-      <c r="D79" s="47">
-        <f>C79</f>
-        <v>5.24</v>
-      </c>
-      <c r="E79" s="47">
-        <f t="shared" ref="E79:F79" si="31">D79</f>
-        <v>5.24</v>
-      </c>
-      <c r="F79" s="47">
-        <f t="shared" si="31"/>
-        <v>5.24</v>
-      </c>
-      <c r="G79" s="42"/>
-      <c r="H79" s="42"/>
-      <c r="I79" s="56"/>
-      <c r="J79" s="58"/>
-      <c r="K79" s="97"/>
-      <c r="L79" s="97"/>
-    </row>
-    <row r="80" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="15"/>
-      <c r="B80" s="37" t="s">
-        <v>64</v>
-      </c>
-      <c r="C80" s="38">
-        <f t="shared" ref="C80:H80" si="32">C79*(1+C79/3)*0.6</f>
-        <v>8.6355200000000014</v>
-      </c>
-      <c r="D80" s="38">
-        <f t="shared" si="32"/>
-        <v>8.6355200000000014</v>
-      </c>
-      <c r="E80" s="38">
-        <f t="shared" si="32"/>
-        <v>8.6355200000000014</v>
-      </c>
-      <c r="F80" s="38">
-        <f t="shared" si="32"/>
-        <v>8.6355200000000014</v>
-      </c>
-      <c r="G80" s="38">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="H80" s="38">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="I80" s="40">
-        <f>SUM(C80:H80)</f>
-        <v>34.542080000000006</v>
-      </c>
-      <c r="J80" s="40">
-        <f>I80+G9</f>
-        <v>77.742080000000001</v>
-      </c>
-      <c r="K80" s="97"/>
-      <c r="L80" s="97"/>
-    </row>
-    <row r="81" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="15"/>
-      <c r="B81" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="C81" s="47">
-        <v>4.3600000000000003</v>
-      </c>
-      <c r="D81" s="47">
-        <f>C81</f>
-        <v>4.3600000000000003</v>
-      </c>
-      <c r="E81" s="47">
-        <f t="shared" ref="E81:F81" si="33">D81</f>
-        <v>4.3600000000000003</v>
-      </c>
-      <c r="F81" s="47">
-        <f t="shared" si="33"/>
-        <v>4.3600000000000003</v>
-      </c>
-      <c r="G81" s="42"/>
-      <c r="H81" s="42"/>
-      <c r="I81" s="56"/>
-      <c r="J81" s="58"/>
-      <c r="K81" s="97"/>
-      <c r="L81" s="97"/>
-    </row>
-    <row r="82" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="20"/>
-      <c r="B82" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="C82" s="38">
-        <f t="shared" ref="C82:H82" si="34">C81*(1+C81/3)*0.6</f>
-        <v>6.4179199999999996</v>
-      </c>
-      <c r="D82" s="38">
-        <f t="shared" si="34"/>
-        <v>6.4179199999999996</v>
-      </c>
-      <c r="E82" s="38">
-        <f t="shared" si="34"/>
-        <v>6.4179199999999996</v>
-      </c>
-      <c r="F82" s="38">
-        <f t="shared" si="34"/>
-        <v>6.4179199999999996</v>
-      </c>
-      <c r="G82" s="38">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="H82" s="38">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="I82" s="40">
-        <f>SUM(C82:H82)</f>
-        <v>25.671679999999999</v>
-      </c>
-      <c r="J82" s="94">
-        <f>I82+G9</f>
-        <v>68.871679999999998</v>
-      </c>
-      <c r="K82" s="49" t="s">
-        <v>101</v>
-      </c>
-      <c r="L82" s="49" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="83" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -7934,7 +5051,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L108"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -7963,9 +5080,7 @@
         <v>29</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="5" t="s">
-        <v>89</v>
-      </c>
+      <c r="C3" s="5"/>
       <c r="D3" s="51"/>
       <c r="E3" s="51"/>
       <c r="F3" s="51"/>
@@ -8685,10 +5800,10 @@
         <v>0</v>
       </c>
       <c r="K38" s="25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L38" s="25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8754,10 +5869,10 @@
         <v>95.77000000000001</v>
       </c>
       <c r="K40" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="L40" s="49" t="s">
         <v>93</v>
-      </c>
-      <c r="L40" s="49" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:12" s="14" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
@@ -8871,10 +5986,10 @@
         <v>75.52000000000001</v>
       </c>
       <c r="K44" s="49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L44" s="49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8939,10 +6054,10 @@
         <v>94.88000000000001</v>
       </c>
       <c r="K46" s="97" t="s">
+        <v>90</v>
+      </c>
+      <c r="L46" s="49" t="s">
         <v>91</v>
-      </c>
-      <c r="L46" s="49" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9105,10 +6220,10 @@
         <v>60</v>
       </c>
       <c r="K52" s="49" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L52" s="49" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9205,10 +6320,10 @@
         <v>0</v>
       </c>
       <c r="K56" s="25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L56" s="25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -9399,10 +6514,10 @@
         <v>75.2</v>
       </c>
       <c r="K62" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="L62" s="49" t="s">
         <v>97</v>
-      </c>
-      <c r="L62" s="49" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="63" spans="1:12" s="14" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
@@ -9507,10 +6622,10 @@
         <v>61.399999999999991</v>
       </c>
       <c r="K66" s="49" t="s">
+        <v>98</v>
+      </c>
+      <c r="L66" s="49" t="s">
         <v>99</v>
-      </c>
-      <c r="L66" s="49" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9645,10 +6760,10 @@
         <v>61.399999999999991</v>
       </c>
       <c r="K70" s="49" t="s">
+        <v>98</v>
+      </c>
+      <c r="L70" s="49" t="s">
         <v>99</v>
-      </c>
-      <c r="L70" s="49" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="71" spans="1:12" s="14" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
@@ -9820,10 +6935,10 @@
         <v>65.599999999999994</v>
       </c>
       <c r="K76" s="49" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L76" s="49" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="77" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -9989,10 +7104,10 @@
         <v>65.599999999999994</v>
       </c>
       <c r="K82" s="49" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L82" s="49" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="83" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
